--- a/accountant-skill/data/output/Mar2025/trial_balance_Mar2025.xlsx
+++ b/accountant-skill/data/output/Mar2025/trial_balance_Mar2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 497,562,751.55 | Cr: 497,562,751.55</t>
+          <t>Dr: 971,128,874.55 | Cr: 971,128,874.55</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 623,471,600.26 | Cr: 623,471,600.26</t>
+          <t>Dr: 1,097,037,723.26 | Cr: 1,097,037,723.26</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4360286.339999999</v>
+        <v>9965463.34</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>8136940.83</v>
@@ -658,7 +658,7 @@
         <v>9965463.779999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2531763.389999999</v>
+        <v>8136940.390000002</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14902650</v>
+        <v>22801950</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>24876371</v>
@@ -680,7 +680,7 @@
         <v>22801950</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16977071</v>
+        <v>24876371</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>16512266.77</v>
+        <v>50973912.77000001</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>53694311.88</v>
@@ -702,7 +702,7 @@
         <v>52187611.7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>18018966.95</v>
+        <v>52480612.95</v>
       </c>
     </row>
     <row r="11">
@@ -771,12 +771,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -788,10 +788,14 @@
           <t>Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>133000000</v>
+      </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>133000000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -803,14 +807,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>554166.67</v>
+        <v>20504166.67</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554166.67</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1108333.34</v>
+        <v>21058333.34</v>
       </c>
     </row>
     <row r="18">
@@ -822,13 +826,15 @@
           <t>Machinery &amp; Equipment</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="4" t="n">
+        <v>66400000</v>
+      </c>
       <c r="D18" s="4" t="n">
         <v>1520000</v>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>1520000</v>
+        <v>67920000</v>
       </c>
     </row>
     <row r="19">
@@ -841,14 +847,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>343758.33</v>
+        <v>12719058.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>356425</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>700183.3300000001</v>
+        <v>13075483.33</v>
       </c>
     </row>
     <row r="20">
@@ -889,12 +895,12 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
     </row>
     <row r="23">
@@ -907,14 +913,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>47500</v>
+        <v>1757500</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>104633.33</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>152133.33</v>
+        <v>1862133.33</v>
       </c>
     </row>
     <row r="24">
@@ -1059,12 +1065,12 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>400000000</v>
+        <v>839530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n">
-        <v>400000000</v>
+        <v>839530823</v>
       </c>
     </row>
     <row r="34">
@@ -1615,7 +1621,7 @@
       </c>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="7" t="n">
-        <v>497562751.55</v>
+        <v>971128874.5500001</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>281173702.22</v>
@@ -1624,7 +1630,7 @@
         <v>281173702.22</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>623471600.26</v>
+        <v>1097037723.26</v>
       </c>
     </row>
   </sheetData>
